--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/186.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/186.xlsx
@@ -426,13 +426,13 @@
         <v>4.289087899668093</v>
       </c>
       <c r="E2">
-        <v>-14.48513678708861</v>
+        <v>-13.90387997736008</v>
       </c>
       <c r="F2">
-        <v>-2.974832335813689</v>
+        <v>-3.42286892786365</v>
       </c>
       <c r="G2">
-        <v>-7.10148549241435</v>
+        <v>-5.75176283387133</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.07830070446564</v>
       </c>
       <c r="E3">
-        <v>-13.32782185579235</v>
+        <v>-14.05594613453765</v>
       </c>
       <c r="F3">
-        <v>-3.538911603852221</v>
+        <v>-3.581356321204265</v>
       </c>
       <c r="G3">
-        <v>-7.140443992320494</v>
+        <v>-6.294553259399155</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.829638520026574</v>
       </c>
       <c r="E4">
-        <v>-14.45642626187998</v>
+        <v>-14.06794659065797</v>
       </c>
       <c r="F4">
-        <v>-3.343093005137043</v>
+        <v>-3.464560659246549</v>
       </c>
       <c r="G4">
-        <v>-6.683929694091614</v>
+        <v>-5.113678354995583</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.576985114577181</v>
       </c>
       <c r="E5">
-        <v>-16.60375618073314</v>
+        <v>-15.52993272471629</v>
       </c>
       <c r="F5">
-        <v>-3.470146340643626</v>
+        <v>-3.644413304640169</v>
       </c>
       <c r="G5">
-        <v>-6.326172279844735</v>
+        <v>-4.751428530451912</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.332890359151418</v>
       </c>
       <c r="E6">
-        <v>-15.85027244754489</v>
+        <v>-15.32486530775295</v>
       </c>
       <c r="F6">
-        <v>-3.634588867242967</v>
+        <v>-3.48693403442876</v>
       </c>
       <c r="G6">
-        <v>-6.2983504551327</v>
+        <v>-5.092467689725473</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.124481161642375</v>
       </c>
       <c r="E7">
-        <v>-16.34641658829926</v>
+        <v>-16.68982888619693</v>
       </c>
       <c r="F7">
-        <v>-3.832930673067072</v>
+        <v>-3.182538835126443</v>
       </c>
       <c r="G7">
-        <v>-6.515168014136187</v>
+        <v>-4.099323891217352</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>2.971020457270264</v>
       </c>
       <c r="E8">
-        <v>-17.16653228803638</v>
+        <v>-16.13004610021277</v>
       </c>
       <c r="F8">
-        <v>-3.687077539353955</v>
+        <v>-3.755195019253561</v>
       </c>
       <c r="G8">
-        <v>-5.984692818014451</v>
+        <v>-4.135114199042413</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>2.88328628340906</v>
       </c>
       <c r="E9">
-        <v>-17.21008262256814</v>
+        <v>-17.19514318681684</v>
       </c>
       <c r="F9">
-        <v>-3.716715696658718</v>
+        <v>-3.846206089064337</v>
       </c>
       <c r="G9">
-        <v>-7.134001670701071</v>
+        <v>-3.682032936537759</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>2.8682314004389</v>
       </c>
       <c r="E10">
-        <v>-17.36233444718003</v>
+        <v>-17.84399199958386</v>
       </c>
       <c r="F10">
-        <v>-3.7352926640339</v>
+        <v>-3.990157291220627</v>
       </c>
       <c r="G10">
-        <v>-5.511092794257393</v>
+        <v>-2.863047007214078</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>2.932362622163079</v>
       </c>
       <c r="E11">
-        <v>-18.05156366267345</v>
+        <v>-17.60588483626056</v>
       </c>
       <c r="F11">
-        <v>-3.834091215798394</v>
+        <v>-3.888750210504717</v>
       </c>
       <c r="G11">
-        <v>-4.059839014570465</v>
+        <v>-2.893884738912389</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.069307853084277</v>
       </c>
       <c r="E12">
-        <v>-18.54548432269005</v>
+        <v>-18.8656791343504</v>
       </c>
       <c r="F12">
-        <v>-3.477162612545338</v>
+        <v>-4.073391647853921</v>
       </c>
       <c r="G12">
-        <v>-4.682797610877281</v>
+        <v>-3.152756157901238</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.264129183126079</v>
       </c>
       <c r="E13">
-        <v>-20.12838071275317</v>
+        <v>-19.35000395794475</v>
       </c>
       <c r="F13">
-        <v>-3.582290719634623</v>
+        <v>-3.723736938764847</v>
       </c>
       <c r="G13">
-        <v>-3.343718356243018</v>
+        <v>-2.115820462999638</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.504978306866773</v>
       </c>
       <c r="E14">
-        <v>-21.33746515890513</v>
+        <v>-19.63338680439675</v>
       </c>
       <c r="F14">
-        <v>-4.071634680592584</v>
+        <v>-3.646809771536468</v>
       </c>
       <c r="G14">
-        <v>-3.511930485638926</v>
+        <v>-2.216626574670446</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.76983626789959</v>
       </c>
       <c r="E15">
-        <v>-21.40800519852261</v>
+        <v>-19.95254006703534</v>
       </c>
       <c r="F15">
-        <v>-3.851737098212829</v>
+        <v>-3.978826053517732</v>
       </c>
       <c r="G15">
-        <v>-3.982133889672692</v>
+        <v>-1.608641575837753</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.032292202716715</v>
       </c>
       <c r="E16">
-        <v>-21.65609764703283</v>
+        <v>-21.30654473838076</v>
       </c>
       <c r="F16">
-        <v>-3.469181292619365</v>
+        <v>-3.639115895099266</v>
       </c>
       <c r="G16">
-        <v>-2.464960527207796</v>
+        <v>-0.5299532805948656</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.27614994224708</v>
       </c>
       <c r="E17">
-        <v>-22.14358787395854</v>
+        <v>-21.85195414786457</v>
       </c>
       <c r="F17">
-        <v>-3.596664550808</v>
+        <v>-3.603321311256897</v>
       </c>
       <c r="G17">
-        <v>-1.849242093995366</v>
+        <v>-0.3129701943144141</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.484136506047223</v>
       </c>
       <c r="E18">
-        <v>-22.99692898748994</v>
+        <v>-23.38093452639237</v>
       </c>
       <c r="F18">
-        <v>-2.966583453216612</v>
+        <v>-3.656111509102504</v>
       </c>
       <c r="G18">
-        <v>-1.001133295562716</v>
+        <v>-0.2304416045659227</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.637939351165007</v>
       </c>
       <c r="E19">
-        <v>-23.5340377041177</v>
+        <v>-22.446135222411</v>
       </c>
       <c r="F19">
-        <v>-3.03674617223373</v>
+        <v>-3.371724696047405</v>
       </c>
       <c r="G19">
-        <v>-2.136726558080136</v>
+        <v>-0.6941497182516378</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.728703851965538</v>
       </c>
       <c r="E20">
-        <v>-25.25643826446111</v>
+        <v>-23.98091204766862</v>
       </c>
       <c r="F20">
-        <v>-3.115002869143602</v>
+        <v>-3.150928335035614</v>
       </c>
       <c r="G20">
-        <v>-1.537845559480439</v>
+        <v>-0.3450427594988734</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.750284180236471</v>
       </c>
       <c r="E21">
-        <v>-24.33742974934449</v>
+        <v>-24.03721909347999</v>
       </c>
       <c r="F21">
-        <v>-2.477622197998745</v>
+        <v>-2.956922204197761</v>
       </c>
       <c r="G21">
-        <v>-1.205652177887811</v>
+        <v>-0.4048477646658074</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.697136658324821</v>
       </c>
       <c r="E22">
-        <v>-24.76561960913976</v>
+        <v>-25.27730547268846</v>
       </c>
       <c r="F22">
-        <v>-2.52070641498575</v>
+        <v>-2.756506166397046</v>
       </c>
       <c r="G22">
-        <v>-1.452261336199201</v>
+        <v>0.2449130083269485</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.569257921584722</v>
       </c>
       <c r="E23">
-        <v>-24.636467530441</v>
+        <v>-24.76187456113541</v>
       </c>
       <c r="F23">
-        <v>-2.833009209515192</v>
+        <v>-2.669761188710688</v>
       </c>
       <c r="G23">
-        <v>-1.588864376786147</v>
+        <v>0.5394125184094347</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.373328913260338</v>
       </c>
       <c r="E24">
-        <v>-25.89403834779308</v>
+        <v>-25.01665556575497</v>
       </c>
       <c r="F24">
-        <v>-1.916813324466466</v>
+        <v>-2.506581922400616</v>
       </c>
       <c r="G24">
-        <v>-0.426829787046568</v>
+        <v>0.4222423801380096</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.115910342834145</v>
       </c>
       <c r="E25">
-        <v>-27.14670482779486</v>
+        <v>-26.28120476155287</v>
       </c>
       <c r="F25">
-        <v>-2.455949621639302</v>
+        <v>-2.722393996749763</v>
       </c>
       <c r="G25">
-        <v>-1.757129474910684</v>
+        <v>-0.2638714934214831</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.804565199348779</v>
       </c>
       <c r="E26">
-        <v>-28.67626937946964</v>
+        <v>-26.38669103508754</v>
       </c>
       <c r="F26">
-        <v>-2.205139024521876</v>
+        <v>-2.779721162860502</v>
       </c>
       <c r="G26">
-        <v>-1.018560007281439</v>
+        <v>-1.14769776767733</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.455229709140293</v>
       </c>
       <c r="E27">
-        <v>-25.99697961893544</v>
+        <v>-25.27317097591945</v>
       </c>
       <c r="F27">
-        <v>-2.765346503319722</v>
+        <v>-2.407177834064675</v>
       </c>
       <c r="G27">
-        <v>-3.437065808813848</v>
+        <v>-0.5473038497661858</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.081782664030717</v>
       </c>
       <c r="E28">
-        <v>-25.68504474386509</v>
+        <v>-24.4491970163278</v>
       </c>
       <c r="F28">
-        <v>-2.130233073756328</v>
+        <v>-2.630216585635845</v>
       </c>
       <c r="G28">
-        <v>-1.750769916929744</v>
+        <v>-1.247596789870377</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.696775428869358</v>
       </c>
       <c r="E29">
-        <v>-25.94690375335863</v>
+        <v>-24.72498108339493</v>
       </c>
       <c r="F29">
-        <v>-2.23203445735597</v>
+        <v>-2.31547756257477</v>
       </c>
       <c r="G29">
-        <v>-1.804582834670597</v>
+        <v>-0.858587825732777</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.319417963708112</v>
       </c>
       <c r="E30">
-        <v>-27.38921819632763</v>
+        <v>-24.62431310620441</v>
       </c>
       <c r="F30">
-        <v>-1.695263149118127</v>
+        <v>-2.559474009436767</v>
       </c>
       <c r="G30">
-        <v>-2.253959596716808</v>
+        <v>-1.895986997009875</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.966424404105528</v>
       </c>
       <c r="E31">
-        <v>-25.92507650864166</v>
+        <v>-23.92819608174533</v>
       </c>
       <c r="F31">
-        <v>-1.704323003402545</v>
+        <v>-2.281651179681452</v>
       </c>
       <c r="G31">
-        <v>-2.448308483145262</v>
+        <v>-1.812369237778963</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.649426006962452</v>
       </c>
       <c r="E32">
-        <v>-26.01971255845395</v>
+        <v>-24.43641766267816</v>
       </c>
       <c r="F32">
-        <v>-2.055839882413113</v>
+        <v>-2.0617246044426</v>
       </c>
       <c r="G32">
-        <v>-2.741718823745328</v>
+        <v>-1.190423668407164</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.381895271240639</v>
       </c>
       <c r="E33">
-        <v>-24.65489841965222</v>
+        <v>-24.39958758357377</v>
       </c>
       <c r="F33">
-        <v>-2.16723293216977</v>
+        <v>-2.266949315016566</v>
       </c>
       <c r="G33">
-        <v>-1.461365336432196</v>
+        <v>-1.537200003100281</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.174568506914058</v>
       </c>
       <c r="E34">
-        <v>-24.14013772225231</v>
+        <v>-23.41606642774388</v>
       </c>
       <c r="F34">
-        <v>-1.910979961215952</v>
+        <v>-2.423403066383309</v>
       </c>
       <c r="G34">
-        <v>-2.151766366465045</v>
+        <v>-1.800772396754896</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.030177278567631</v>
       </c>
       <c r="E35">
-        <v>-24.33669613655525</v>
+        <v>-23.69728919209421</v>
       </c>
       <c r="F35">
-        <v>-1.740987373017854</v>
+        <v>-2.204608041016681</v>
       </c>
       <c r="G35">
-        <v>-2.678603273039123</v>
+        <v>-1.247202834951204</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.9489267210236204</v>
       </c>
       <c r="E36">
-        <v>-24.34151896137341</v>
+        <v>-22.72349972690681</v>
       </c>
       <c r="F36">
-        <v>-1.945294252509518</v>
+        <v>-2.223826993129033</v>
       </c>
       <c r="G36">
-        <v>-2.168478000347286</v>
+        <v>-2.093441175154165</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.9316848904445718</v>
       </c>
       <c r="E37">
-        <v>-23.56631213837036</v>
+        <v>-22.93330392768217</v>
       </c>
       <c r="F37">
-        <v>-1.971118606291793</v>
+        <v>-2.238901623125178</v>
       </c>
       <c r="G37">
-        <v>-3.093997285124714</v>
+        <v>-2.254651500734515</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.9715245487419879</v>
       </c>
       <c r="E38">
-        <v>-23.19245038124512</v>
+        <v>-21.64211824777115</v>
       </c>
       <c r="F38">
-        <v>-1.329986259179657</v>
+        <v>-1.870715506868076</v>
       </c>
       <c r="G38">
-        <v>-2.323633338136309</v>
+        <v>-1.85907772479254</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.057255935039293</v>
       </c>
       <c r="E39">
-        <v>-21.88147979839459</v>
+        <v>-21.22316647495153</v>
       </c>
       <c r="F39">
-        <v>-1.950223038556175</v>
+        <v>-1.690239929187551</v>
       </c>
       <c r="G39">
-        <v>-3.112029826677124</v>
+        <v>-0.8964273612466467</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.181324049654464</v>
       </c>
       <c r="E40">
-        <v>-21.64554630259496</v>
+        <v>-21.30100641466938</v>
       </c>
       <c r="F40">
-        <v>-2.31972957245334</v>
+        <v>-2.064111959297468</v>
       </c>
       <c r="G40">
-        <v>-2.810386159320891</v>
+        <v>-1.815914832051523</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.331053399020707</v>
       </c>
       <c r="E41">
-        <v>-20.51665660264484</v>
+        <v>-20.37868305657914</v>
       </c>
       <c r="F41">
-        <v>-1.327135846946624</v>
+        <v>-1.736044504725349</v>
       </c>
       <c r="G41">
-        <v>-2.805724911201597</v>
+        <v>-1.57590690154544</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.491256968073661</v>
       </c>
       <c r="E42">
-        <v>-22.08200968440224</v>
+        <v>-19.18703776383072</v>
       </c>
       <c r="F42">
-        <v>-1.941226968561773</v>
+        <v>-1.944193352231198</v>
       </c>
       <c r="G42">
-        <v>-2.603900812945468</v>
+        <v>-1.514277785786368</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.652263033752081</v>
       </c>
       <c r="E43">
-        <v>-21.04742092718785</v>
+        <v>-20.24970305989267</v>
       </c>
       <c r="F43">
-        <v>-1.765365397314841</v>
+        <v>-1.880670826314921</v>
       </c>
       <c r="G43">
-        <v>-3.207128557838228</v>
+        <v>-1.961208054679056</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.804055502066435</v>
       </c>
       <c r="E44">
-        <v>-20.37568973526007</v>
+        <v>-18.85244693329999</v>
       </c>
       <c r="F44">
-        <v>-1.731539014421523</v>
+        <v>-1.615660355178705</v>
       </c>
       <c r="G44">
-        <v>-3.153544067739585</v>
+        <v>-1.20797618085638</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.936508387949713</v>
       </c>
       <c r="E45">
-        <v>-19.20602112687088</v>
+        <v>-18.27112672493535</v>
       </c>
       <c r="F45">
-        <v>-1.511550311627461</v>
+        <v>-1.755296591533813</v>
       </c>
       <c r="G45">
-        <v>-2.470237536797394</v>
+        <v>-1.712125918849831</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.043787359355259</v>
       </c>
       <c r="E46">
-        <v>-18.39229057548457</v>
+        <v>-17.34004982658828</v>
       </c>
       <c r="F46">
-        <v>-1.305484808139653</v>
+        <v>-1.879444014191374</v>
       </c>
       <c r="G46">
-        <v>-2.703866046049301</v>
+        <v>-1.33343592515814</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.121457191856563</v>
       </c>
       <c r="E47">
-        <v>-17.24116153968279</v>
+        <v>-17.46810601457718</v>
       </c>
       <c r="F47">
-        <v>-1.702336578370632</v>
+        <v>-1.973450460530674</v>
       </c>
       <c r="G47">
-        <v>-2.258587739380709</v>
+        <v>-1.911195643217287</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.164963378572092</v>
       </c>
       <c r="E48">
-        <v>-16.59259349230424</v>
+        <v>-17.01892667775636</v>
       </c>
       <c r="F48">
-        <v>-0.8512147513836266</v>
+        <v>-1.935851692485007</v>
       </c>
       <c r="G48">
-        <v>-3.059769554794189</v>
+        <v>-1.848099955784317</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.171235831047802</v>
       </c>
       <c r="E49">
-        <v>-17.95210931651699</v>
+        <v>-17.07453181009655</v>
       </c>
       <c r="F49">
-        <v>-1.392415340124239</v>
+        <v>-1.589553528112076</v>
       </c>
       <c r="G49">
-        <v>-2.919918869033217</v>
+        <v>-1.78803672806532</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.139604648069602</v>
       </c>
       <c r="E50">
-        <v>-15.25561135475365</v>
+        <v>-14.79107596257282</v>
       </c>
       <c r="F50">
-        <v>-0.9506229815565812</v>
+        <v>-1.46526859646565</v>
       </c>
       <c r="G50">
-        <v>-3.563922603333181</v>
+        <v>-1.232076952382274</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.069378050492704</v>
       </c>
       <c r="E51">
-        <v>-16.82358189448749</v>
+        <v>-15.6889274471256</v>
       </c>
       <c r="F51">
-        <v>-1.827656969270558</v>
+        <v>-2.016392198324397</v>
       </c>
       <c r="G51">
-        <v>-3.647235792374479</v>
+        <v>-2.820824309406213</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.960633037205376</v>
       </c>
       <c r="E52">
-        <v>-15.15824463511473</v>
+        <v>-14.6448877646572</v>
       </c>
       <c r="F52">
-        <v>-1.467216916597034</v>
+        <v>-1.613060938268721</v>
       </c>
       <c r="G52">
-        <v>-3.53885184196428</v>
+        <v>-1.659812678238268</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.816339758083224</v>
       </c>
       <c r="E53">
-        <v>-14.05002289053562</v>
+        <v>-13.88303993997678</v>
       </c>
       <c r="F53">
-        <v>-1.01293857616698</v>
+        <v>-1.768740166113846</v>
       </c>
       <c r="G53">
-        <v>-2.726384376807424</v>
+        <v>-1.676004556470844</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.639655628221818</v>
       </c>
       <c r="E54">
-        <v>-14.33513561405854</v>
+        <v>-14.00611933503125</v>
       </c>
       <c r="F54">
-        <v>-1.075512621407051</v>
+        <v>-1.768825487956334</v>
       </c>
       <c r="G54">
-        <v>-3.896486766026207</v>
+        <v>-2.164336507877658</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.434971165025672</v>
       </c>
       <c r="E55">
-        <v>-14.64797165545642</v>
+        <v>-14.6473059697773</v>
       </c>
       <c r="F55">
-        <v>-1.35727185306047</v>
+        <v>-1.575221115308839</v>
       </c>
       <c r="G55">
-        <v>-3.592078793144682</v>
+        <v>-2.722808987625011</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.208622166886679</v>
       </c>
       <c r="E56">
-        <v>-13.93941038442426</v>
+        <v>-13.36027742900532</v>
       </c>
       <c r="F56">
-        <v>-1.219720617458209</v>
+        <v>-1.806393606408097</v>
       </c>
       <c r="G56">
-        <v>-4.676484400533892</v>
+        <v>-2.506497942089031</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.9670717169837163</v>
       </c>
       <c r="E57">
-        <v>-13.70049715272759</v>
+        <v>-12.97546129325552</v>
       </c>
       <c r="F57">
-        <v>-1.155281917194436</v>
+        <v>-1.769376352279196</v>
       </c>
       <c r="G57">
-        <v>-4.437446459870816</v>
+        <v>-2.645957983476369</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.7166048196648902</v>
       </c>
       <c r="E58">
-        <v>-12.41130852985395</v>
+        <v>-13.47431798994048</v>
       </c>
       <c r="F58">
-        <v>-1.584783788606757</v>
+        <v>-1.485577680080085</v>
       </c>
       <c r="G58">
-        <v>-3.735246645536004</v>
+        <v>-2.413954952084245</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.4628691897653049</v>
       </c>
       <c r="E59">
-        <v>-12.70722166388517</v>
+        <v>-12.81730886701164</v>
       </c>
       <c r="F59">
-        <v>-1.51072442932687</v>
+        <v>-1.512459030668332</v>
       </c>
       <c r="G59">
-        <v>-3.983325686066829</v>
+        <v>-2.604639064600726</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.2111639602589261</v>
       </c>
       <c r="E60">
-        <v>-12.41264442968621</v>
+        <v>-13.33915662623354</v>
       </c>
       <c r="F60">
-        <v>-1.158036238808744</v>
+        <v>-1.535172864853094</v>
       </c>
       <c r="G60">
-        <v>-4.765445380265187</v>
+        <v>-2.591125417709421</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.03455134974643211</v>
       </c>
       <c r="E61">
-        <v>-12.81868552310997</v>
+        <v>-12.68980968132568</v>
       </c>
       <c r="F61">
-        <v>-1.463896820046614</v>
+        <v>-1.806355501507569</v>
       </c>
       <c r="G61">
-        <v>-3.483247919086681</v>
+        <v>-3.242246824918817</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.271956689499468</v>
       </c>
       <c r="E62">
-        <v>-12.84667149247737</v>
+        <v>-11.75953885135198</v>
       </c>
       <c r="F62">
-        <v>-0.7585784247285579</v>
+        <v>-1.507907980157351</v>
       </c>
       <c r="G62">
-        <v>-4.651883736631567</v>
+        <v>-3.052294342966515</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.4988853829742342</v>
       </c>
       <c r="E63">
-        <v>-13.78149343882878</v>
+        <v>-11.75099814937351</v>
       </c>
       <c r="F63">
-        <v>-0.9308896132870914</v>
+        <v>-1.244801925680172</v>
       </c>
       <c r="G63">
-        <v>-4.350355938369209</v>
+        <v>-2.517128103815631</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.7148089674211092</v>
       </c>
       <c r="E64">
-        <v>-12.28289459241844</v>
+        <v>-11.51830251248937</v>
       </c>
       <c r="F64">
-        <v>-0.9089403622151129</v>
+        <v>-1.663447213911403</v>
       </c>
       <c r="G64">
-        <v>-3.973569508362597</v>
+        <v>-2.77373510965562</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.9194003896151169</v>
       </c>
       <c r="E65">
-        <v>-12.30661473927062</v>
+        <v>-11.67371521195861</v>
       </c>
       <c r="F65">
-        <v>-1.586905237525326</v>
+        <v>-1.27512182935744</v>
       </c>
       <c r="G65">
-        <v>-4.826773236380185</v>
+        <v>-3.077414762518505</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.112881778589723</v>
       </c>
       <c r="E66">
-        <v>-13.0122913723599</v>
+        <v>-12.02968043980555</v>
       </c>
       <c r="F66">
-        <v>-1.620715053070588</v>
+        <v>-1.303349276975236</v>
       </c>
       <c r="G66">
-        <v>-5.139570131658224</v>
+        <v>-2.578485754840484</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.296011230820115</v>
       </c>
       <c r="E67">
-        <v>-12.96860971208191</v>
+        <v>-11.78228537629251</v>
       </c>
       <c r="F67">
-        <v>-1.256012221742258</v>
+        <v>-1.932648395738381</v>
       </c>
       <c r="G67">
-        <v>-4.697155446881101</v>
+        <v>-3.180796478618865</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.467715684480053</v>
       </c>
       <c r="E68">
-        <v>-11.70615719974956</v>
+        <v>-11.20965530954858</v>
       </c>
       <c r="F68">
-        <v>-1.375122342223396</v>
+        <v>-1.940206419921524</v>
       </c>
       <c r="G68">
-        <v>-4.816252322656381</v>
+        <v>-3.03878069607521</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.629051794060666</v>
       </c>
       <c r="E69">
-        <v>-12.52266370570256</v>
+        <v>-11.60997694030065</v>
       </c>
       <c r="F69">
-        <v>-1.62756565149174</v>
+        <v>-1.350206707481993</v>
       </c>
       <c r="G69">
-        <v>-4.723811959563312</v>
+        <v>-2.663970661755544</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.780246899225499</v>
       </c>
       <c r="E70">
-        <v>-11.22220823949784</v>
+        <v>-12.79706658819735</v>
       </c>
       <c r="F70">
-        <v>-1.536161107164634</v>
+        <v>-1.872363957999647</v>
       </c>
       <c r="G70">
-        <v>-4.854515607999278</v>
+        <v>-3.383878584179917</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.9191416428262</v>
       </c>
       <c r="E71">
-        <v>-13.21004530380086</v>
+        <v>-11.42054634408579</v>
       </c>
       <c r="F71">
-        <v>-1.80703641951267</v>
+        <v>-1.717894146562609</v>
       </c>
       <c r="G71">
-        <v>-4.762446026006607</v>
+        <v>-3.144449999143207</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.044458064055943</v>
       </c>
       <c r="E72">
-        <v>-13.95267428479272</v>
+        <v>-11.44446574379431</v>
       </c>
       <c r="F72">
-        <v>-1.925183977071755</v>
+        <v>-2.199331340660848</v>
       </c>
       <c r="G72">
-        <v>-3.584659860591175</v>
+        <v>-2.55247479853843</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.15438210074278</v>
       </c>
       <c r="E73">
-        <v>-10.17689605583329</v>
+        <v>-11.17225464271923</v>
       </c>
       <c r="F73">
-        <v>-1.902843736585655</v>
+        <v>-2.277165570195293</v>
       </c>
       <c r="G73">
-        <v>-3.977711000832226</v>
+        <v>-2.984732729601069</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.245207303445411</v>
       </c>
       <c r="E74">
-        <v>-12.26308704710889</v>
+        <v>-12.6072872994839</v>
       </c>
       <c r="F74">
-        <v>-2.069089619020891</v>
+        <v>-2.402957302147412</v>
       </c>
       <c r="G74">
-        <v>-4.831424552862861</v>
+        <v>-3.379333205154498</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.312964420607529</v>
       </c>
       <c r="E75">
-        <v>-13.23889168322972</v>
+        <v>-12.59127461539278</v>
       </c>
       <c r="F75">
-        <v>-2.151054088425693</v>
+        <v>-2.170712075261528</v>
       </c>
       <c r="G75">
-        <v>-4.11264883701292</v>
+        <v>-2.557427374665179</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.35582962877293</v>
       </c>
       <c r="E76">
-        <v>-13.59099412274811</v>
+        <v>-13.24890866773468</v>
       </c>
       <c r="F76">
-        <v>-1.941867296564137</v>
+        <v>-2.543602489999128</v>
       </c>
       <c r="G76">
-        <v>-5.249364374468152</v>
+        <v>-2.745095580195384</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.371074166303455</v>
       </c>
       <c r="E77">
-        <v>-14.42344085720811</v>
+        <v>-13.28012796754356</v>
       </c>
       <c r="F77">
-        <v>-2.166687038051325</v>
+        <v>-2.703060729935825</v>
       </c>
       <c r="G77">
-        <v>-3.100366774742272</v>
+        <v>-2.901412919468692</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.355986230035675</v>
       </c>
       <c r="E78">
-        <v>-13.69732269244821</v>
+        <v>-14.35838932808793</v>
       </c>
       <c r="F78">
-        <v>-1.463274716127111</v>
+        <v>-2.876803337366396</v>
       </c>
       <c r="G78">
-        <v>-4.226180685736685</v>
+        <v>-2.567769518929862</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.311817133915507</v>
       </c>
       <c r="E79">
-        <v>-14.69060270976463</v>
+        <v>-15.45154936811753</v>
       </c>
       <c r="F79">
-        <v>-2.460184235802413</v>
+        <v>-2.950938078079938</v>
       </c>
       <c r="G79">
-        <v>-3.194614695699783</v>
+        <v>-2.209879682861412</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.239367732724706</v>
       </c>
       <c r="E80">
-        <v>-15.78113170639578</v>
+        <v>-14.84827964623771</v>
       </c>
       <c r="F80">
-        <v>-2.514108468622452</v>
+        <v>-2.941311620492005</v>
       </c>
       <c r="G80">
-        <v>-3.379627843707493</v>
+        <v>-2.620168833725447</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.138811244789513</v>
       </c>
       <c r="E81">
-        <v>-15.21331993599602</v>
+        <v>-15.10997110219296</v>
       </c>
       <c r="F81">
-        <v>-1.954248904133781</v>
+        <v>-2.83291394726387</v>
       </c>
       <c r="G81">
-        <v>-3.715241018842188</v>
+        <v>-2.268105557806113</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.013827587651191</v>
       </c>
       <c r="E82">
-        <v>-17.04946670646409</v>
+        <v>-15.43800017388658</v>
       </c>
       <c r="F82">
-        <v>-2.090587409858343</v>
+        <v>-2.850846444799673</v>
       </c>
       <c r="G82">
-        <v>-4.018331394599083</v>
+        <v>-1.667625565710948</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.868454041660437</v>
       </c>
       <c r="E83">
-        <v>-18.05266861033132</v>
+        <v>-17.30571040818812</v>
       </c>
       <c r="F83">
-        <v>-2.834710676160542</v>
+        <v>-3.196484400352573</v>
       </c>
       <c r="G83">
-        <v>-3.751716609593878</v>
+        <v>-2.217040392862855</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.705839889611616</v>
       </c>
       <c r="E84">
-        <v>-19.38652157234261</v>
+        <v>-18.48855687593963</v>
       </c>
       <c r="F84">
-        <v>-2.948894495697231</v>
+        <v>-3.28482978386114</v>
       </c>
       <c r="G84">
-        <v>-3.221208308016749</v>
+        <v>-2.05472103452685</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.5307140301658</v>
       </c>
       <c r="E85">
-        <v>-19.46336071930476</v>
+        <v>-18.92346699116229</v>
       </c>
       <c r="F85">
-        <v>-2.854016606850187</v>
+        <v>-3.22115235324054</v>
       </c>
       <c r="G85">
-        <v>-2.84436559873597</v>
+        <v>-1.245898480008731</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.349412120323313</v>
       </c>
       <c r="E86">
-        <v>-20.50517239256139</v>
+        <v>-20.7571593287182</v>
       </c>
       <c r="F86">
-        <v>-3.315413108372498</v>
+        <v>-3.530438233688985</v>
       </c>
       <c r="G86">
-        <v>-3.218775057045384</v>
+        <v>-1.516075412014192</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.166930627570418</v>
       </c>
       <c r="E87">
-        <v>-22.05664570148528</v>
+        <v>-21.68500289662379</v>
       </c>
       <c r="F87">
-        <v>-3.361317087998632</v>
+        <v>-3.839956057010215</v>
       </c>
       <c r="G87">
-        <v>-2.52444440945742</v>
+        <v>-1.652344087501672</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.9883222763159487</v>
       </c>
       <c r="E88">
-        <v>-23.66001079406307</v>
+        <v>-22.82911279771369</v>
       </c>
       <c r="F88">
-        <v>-3.434981316027384</v>
+        <v>-3.326908362821146</v>
       </c>
       <c r="G88">
-        <v>-3.682380543819382</v>
+        <v>-1.078580197908426</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.8227838498176279</v>
       </c>
       <c r="E89">
-        <v>-23.24594524469773</v>
+        <v>-23.80040254524887</v>
       </c>
       <c r="F89">
-        <v>-3.030009060146762</v>
+        <v>-3.600134581858327</v>
       </c>
       <c r="G89">
-        <v>-2.336090921000586</v>
+        <v>-1.90645494200505</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.6776819815236438</v>
       </c>
       <c r="E90">
-        <v>-25.64026719287724</v>
+        <v>-26.26241159442104</v>
       </c>
       <c r="F90">
-        <v>-2.722481803694459</v>
+        <v>-4.252669406269998</v>
       </c>
       <c r="G90">
-        <v>-3.517220737410682</v>
+        <v>-1.908977577705975</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.5589398616808547</v>
       </c>
       <c r="E91">
-        <v>-25.41436879547862</v>
+        <v>-26.81439181968998</v>
       </c>
       <c r="F91">
-        <v>-2.870624544908915</v>
+        <v>-4.233066091682748</v>
       </c>
       <c r="G91">
-        <v>-2.143486692071328</v>
+        <v>-1.643478446547504</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.4763975620001386</v>
       </c>
       <c r="E92">
-        <v>-28.04810210749565</v>
+        <v>-28.15323968853173</v>
       </c>
       <c r="F92">
-        <v>-3.391285763897113</v>
+        <v>-4.285578786448418</v>
       </c>
       <c r="G92">
-        <v>-3.053025973530694</v>
+        <v>-2.324841687258143</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.4370329010098061</v>
       </c>
       <c r="E93">
-        <v>-30.34084132673511</v>
+        <v>-31.31687691503032</v>
       </c>
       <c r="F93">
-        <v>-3.76285244752504</v>
+        <v>-4.520776314757878</v>
       </c>
       <c r="G93">
-        <v>-1.99244305184208</v>
+        <v>-2.687776794728443</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.4431176246493499</v>
       </c>
       <c r="E94">
-        <v>-32.33635189024411</v>
+        <v>-31.92590006313689</v>
       </c>
       <c r="F94">
-        <v>-4.13487887506152</v>
+        <v>-4.550384650836141</v>
       </c>
       <c r="G94">
-        <v>-3.384649941290567</v>
+        <v>-2.139050561048705</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.4983779158919983</v>
       </c>
       <c r="E95">
-        <v>-33.81619832578868</v>
+        <v>-35.03976256758017</v>
       </c>
       <c r="F95">
-        <v>-4.207373448317519</v>
+        <v>-4.425830499783804</v>
       </c>
       <c r="G95">
-        <v>-3.798524412973633</v>
+        <v>-2.494037048679214</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.6056477775741845</v>
       </c>
       <c r="E96">
-        <v>-36.36698357940722</v>
+        <v>-35.64847551521721</v>
       </c>
       <c r="F96">
-        <v>-4.01696657384483</v>
+        <v>-5.092429345960205</v>
       </c>
       <c r="G96">
-        <v>-3.818675703671177</v>
+        <v>-2.728926875781584</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.7578728029561093</v>
       </c>
       <c r="E97">
-        <v>-38.61837103824563</v>
+        <v>-38.43886232858159</v>
       </c>
       <c r="F97">
-        <v>-4.147503194280184</v>
+        <v>-5.214335206425792</v>
       </c>
       <c r="G97">
-        <v>-4.876159954735033</v>
+        <v>-2.924427832057705</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.9566522459438299</v>
       </c>
       <c r="E98">
-        <v>-41.04615614510483</v>
+        <v>-39.41377032684889</v>
       </c>
       <c r="F98">
-        <v>-4.570032697263143</v>
+        <v>-5.287222425830718</v>
       </c>
       <c r="G98">
-        <v>-4.788526503764985</v>
+        <v>-3.543602474813134</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.189788613375355</v>
       </c>
       <c r="E99">
-        <v>-43.00345544493712</v>
+        <v>-42.2858870391037</v>
       </c>
       <c r="F99">
-        <v>-4.731884090626527</v>
+        <v>-5.29898192948086</v>
       </c>
       <c r="G99">
-        <v>-5.352431588742283</v>
+        <v>-3.236996299693533</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.464182358379724</v>
       </c>
       <c r="E100">
-        <v>-44.54342869411853</v>
+        <v>-44.98173290060993</v>
       </c>
       <c r="F100">
-        <v>-4.985246887711978</v>
+        <v>-5.992627799726067</v>
       </c>
       <c r="G100">
-        <v>-5.685436053992031</v>
+        <v>-4.311473581010468</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.751867338968756</v>
       </c>
       <c r="E101">
-        <v>-46.14907387335919</v>
+        <v>-45.99714357040185</v>
       </c>
       <c r="F101">
-        <v>-4.94455582415166</v>
+        <v>-5.768031717437635</v>
       </c>
       <c r="G101">
-        <v>-5.236420141409602</v>
+        <v>-4.389086010633141</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.085671091468216</v>
       </c>
       <c r="E102">
-        <v>-46.67413458488954</v>
+        <v>-48.20500107284153</v>
       </c>
       <c r="F102">
-        <v>-5.565022061298754</v>
+        <v>-5.988014621659877</v>
       </c>
       <c r="G102">
-        <v>-6.242849159166818</v>
+        <v>-4.181524736957456</v>
       </c>
     </row>
   </sheetData>
